--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_30-12-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_30-12-2025.xlsx
@@ -232,9 +232,6 @@
     <t>POA or OOS</t>
   </si>
   <si>
-    <t>Error: list index out of range</t>
-  </si>
-  <si>
     <t>£18.75</t>
   </si>
   <si>
@@ -365,6 +362,9 @@
   </si>
   <si>
     <t>£40.63</t>
+  </si>
+  <si>
+    <t>POA</t>
   </si>
   <si>
     <t>Price Not Found</t>
@@ -801,22 +801,22 @@
         <v>57</v>
       </c>
       <c r="I2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" t="s">
         <v>72</v>
       </c>
-      <c r="J2" t="s">
-        <v>73</v>
-      </c>
       <c r="K2" t="s">
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" t="s">
         <v>117</v>
@@ -848,22 +848,22 @@
         <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M3" t="s">
         <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O3" t="s">
         <v>117</v>
@@ -895,22 +895,22 @@
         <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s">
         <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" t="s">
         <v>117</v>
@@ -942,22 +942,22 @@
         <v>57</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O5" t="s">
         <v>117</v>
@@ -989,22 +989,22 @@
         <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" t="s">
         <v>117</v>
@@ -1036,22 +1036,22 @@
         <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O7" t="s">
         <v>117</v>
@@ -1083,22 +1083,22 @@
         <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O8" t="s">
         <v>117</v>
@@ -1130,22 +1130,22 @@
         <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O9" t="s">
         <v>117</v>
@@ -1177,22 +1177,22 @@
         <v>57</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s">
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" t="s">
         <v>117</v>
@@ -1224,22 +1224,22 @@
         <v>57</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s">
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O11" t="s">
         <v>117</v>
@@ -1271,22 +1271,22 @@
         <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M12" t="s">
         <v>57</v>
       </c>
       <c r="N12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O12" t="s">
         <v>117</v>
@@ -1318,22 +1318,22 @@
         <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s">
         <v>57</v>
       </c>
       <c r="N13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O13" t="s">
         <v>117</v>
@@ -1365,7 +1365,7 @@
         <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
         <v>57</v>
@@ -1380,7 +1380,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1412,22 +1412,22 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M15" t="s">
         <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O15" t="s">
         <v>117</v>
@@ -1459,22 +1459,22 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M16" t="s">
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O16" t="s">
         <v>117</v>
@@ -1506,22 +1506,22 @@
         <v>57</v>
       </c>
       <c r="I17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L17" t="s">
+        <v>115</v>
+      </c>
+      <c r="M17" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" t="s">
         <v>116</v>
-      </c>
-      <c r="M17" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" t="s">
-        <v>117</v>
       </c>
       <c r="O17" t="s">
         <v>117</v>
